--- a/data/trans_camb/P16A_n_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,49</t>
+          <t>0,77; 5,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,66</t>
+          <t>-0,79; 4,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 12,27</t>
+          <t>1,97; 12,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 9,27</t>
+          <t>0,4; 9,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 4,07</t>
+          <t>-4,19; 4,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 9,51</t>
+          <t>-2,49; 9,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,41</t>
+          <t>1,43; 6,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,93</t>
+          <t>-1,85; 2,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 8,5</t>
+          <t>0,7; 8,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 362,93</t>
+          <t>16,94; 360,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 215,47</t>
+          <t>-27,51; 238,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,1; 800,56</t>
+          <t>47,29; 731,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 101,48</t>
+          <t>0,78; 101,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 43,1</t>
+          <t>-33,92; 49,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 100,92</t>
+          <t>-19,93; 99,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,86; 113,91</t>
+          <t>18,47; 115,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 50,25</t>
+          <t>-23,68; 53,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 140,07</t>
+          <t>9,11; 142,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,84</t>
+          <t>3,4; 9,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,53</t>
+          <t>1,66; 7,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 13,17</t>
+          <t>4,24; 13,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,84</t>
+          <t>2,03; 10,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,83</t>
+          <t>-3,21; 4,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 7,68</t>
+          <t>-4,77; 7,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,57</t>
+          <t>3,64; 8,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,29</t>
+          <t>0,32; 4,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,58</t>
+          <t>2,15; 9,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76,09; 300,39</t>
+          <t>74,71; 344,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,18; 231,49</t>
+          <t>31,18; 234,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98,68; 437,35</t>
+          <t>92,4; 441,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 88,79</t>
+          <t>12,12; 88,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 38,55</t>
+          <t>-21,26; 38,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 59,67</t>
+          <t>-30,24; 58,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,06; 116,72</t>
+          <t>37,1; 121,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 69,82</t>
+          <t>3,54; 69,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 124,98</t>
+          <t>22,96; 124,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,6</t>
+          <t>0,84; 7,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,16</t>
+          <t>-1,4; 5,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 10,36</t>
+          <t>2,41; 9,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 14,38</t>
+          <t>5,19; 13,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,99</t>
+          <t>-0,64; 6,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,52</t>
+          <t>-0,11; 10,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,15</t>
+          <t>4,2; 9,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,04</t>
+          <t>-0,42; 4,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,97</t>
+          <t>3,04; 8,78</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,57; 119,63</t>
+          <t>7,05; 111,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 78,47</t>
+          <t>-14,33; 77,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,22; 143,57</t>
+          <t>24,16; 149,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,87; 113,9</t>
+          <t>30,72; 112,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 55,29</t>
+          <t>-4,59; 54,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,04; 79,66</t>
+          <t>2,03; 80,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,39; 98,39</t>
+          <t>32,9; 93,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 46,2</t>
+          <t>-3,68; 44,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,76; 86,45</t>
+          <t>24,14; 84,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,27</t>
+          <t>-2,79; 7,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 8,16</t>
+          <t>-0,75; 8,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 12,87</t>
+          <t>-8,16; 13,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,2</t>
+          <t>4,03; 15,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 9,35</t>
+          <t>-1,02; 9,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 14,46</t>
+          <t>3,72; 14,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,86</t>
+          <t>2,85; 9,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,78</t>
+          <t>0,69; 7,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 12,01</t>
+          <t>-4,53; 12,33</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 57,63</t>
+          <t>-15,63; 54,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 63,56</t>
+          <t>-4,57; 62,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 89,57</t>
+          <t>-48,59; 94,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,84; 73,83</t>
+          <t>15,22; 75,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 46,91</t>
+          <t>-3,93; 43,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 68,82</t>
+          <t>15,4; 73,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,47; 55,98</t>
+          <t>12,59; 54,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 43,99</t>
+          <t>3,44; 44,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 65,63</t>
+          <t>-20,2; 66,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,32</t>
+          <t>-0,3; 13,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 6,66</t>
+          <t>-5,84; 7,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 14,95</t>
+          <t>2,08; 14,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 18,8</t>
+          <t>5,58; 19,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 15,85</t>
+          <t>0,31; 14,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 13,24</t>
+          <t>1,7; 13,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 14,94</t>
+          <t>4,28; 14,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 9,49</t>
+          <t>-0,58; 9,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,76</t>
+          <t>3,25; 11,74</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 43,15</t>
+          <t>-1,3; 43,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 22,36</t>
+          <t>-15,24; 25,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4,62; 48,64</t>
+          <t>5,5; 47,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,27; 46,95</t>
+          <t>11,53; 46,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,17; 38,88</t>
+          <t>0,68; 36,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,6; 33,33</t>
+          <t>3,44; 34,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,55; 41,46</t>
+          <t>10,19; 37,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 26,41</t>
+          <t>-1,75; 25,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7,61; 32,42</t>
+          <t>7,82; 31,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>14,43; 30,45</t>
+          <t>14,49; 30,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,02; 16,06</t>
+          <t>0,77; 16,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,9; 15,49</t>
+          <t>1,74; 15,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,45</t>
+          <t>2,03; 15,26</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 6,04</t>
+          <t>-7,27; 6,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 27,83</t>
+          <t>-0,5; 28,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,15; 19,96</t>
+          <t>9,42; 20,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,37</t>
+          <t>-1,92; 8,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,21; 28,76</t>
+          <t>3,41; 27,33</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30,06; 77,5</t>
+          <t>30,15; 77,74</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 39,02</t>
+          <t>1,55; 41,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4,38; 39,72</t>
+          <t>3,59; 38,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,59; 25,13</t>
+          <t>2,84; 24,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 9,89</t>
+          <t>-10,75; 10,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,05; 46,12</t>
+          <t>-0,89; 48,35</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,1; 37,81</t>
+          <t>15,88; 38,62</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 15,9</t>
+          <t>-3,41; 16,77</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,66; 53,32</t>
+          <t>5,83; 49,61</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,59; 22,35</t>
+          <t>6,53; 22,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 14,51</t>
+          <t>-2,48; 13,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 9,48</t>
+          <t>-4,61; 10,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,96; 20,6</t>
+          <t>8,31; 20,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 11,37</t>
+          <t>-2,08; 11,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,25</t>
+          <t>2,3; 14,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,96; 18,83</t>
+          <t>9,33; 19,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,01; 10,14</t>
+          <t>0,37; 10,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,5</t>
+          <t>0,93; 10,32</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>8,19; 36,99</t>
+          <t>9,36; 37,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 24,44</t>
+          <t>-3,34; 23,11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 15,68</t>
+          <t>-6,63; 18,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,33; 29,94</t>
+          <t>10,67; 30,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 16,34</t>
+          <t>-2,66; 16,45</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,41; 20,91</t>
+          <t>3,1; 20,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,46; 28,43</t>
+          <t>12,65; 29,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,1; 15,17</t>
+          <t>0,52; 15,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,55; 16,24</t>
+          <t>1,35; 15,55</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,04</t>
+          <t>5,76; 9,61</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,53</t>
+          <t>3,58; 7,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,69; 13,37</t>
+          <t>4,11; 13,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,57</t>
+          <t>7,8; 12,55</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,14</t>
+          <t>2,72; 7,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,83</t>
+          <t>8,74; 23,49</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,69</t>
+          <t>7,51; 10,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,86</t>
+          <t>3,75; 6,74</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>8,23; 17,89</t>
+          <t>8,36; 17,13</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>31,84; 60,41</t>
+          <t>31,36; 57,97</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>19,22; 45,27</t>
+          <t>19,65; 44,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27,24; 79,39</t>
+          <t>23,44; 77,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25,37; 43,76</t>
+          <t>25,13; 43,69</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,59; 24,98</t>
+          <t>8,55; 25,51</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,98; 81,85</t>
+          <t>28,86; 79,74</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,51; 46,76</t>
+          <t>30,29; 46,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15,0; 29,42</t>
+          <t>14,9; 29,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34,25; 76,79</t>
+          <t>34,48; 72,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>5,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,65</t>
+          <t>0,45; 5,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,05</t>
+          <t>-0,83; 3,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 12,82</t>
+          <t>2,77; 12,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 9,19</t>
+          <t>0,32; 9,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,24</t>
+          <t>-4,2; 4,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,16</t>
+          <t>-1,59; 10,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,28</t>
+          <t>1,64; 6,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,93</t>
+          <t>-1,78; 2,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,66</t>
+          <t>1,89; 9,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>239,8%</t>
+          <t>279,4%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 360,69</t>
+          <t>3,41; 368,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 238,29</t>
+          <t>-32,48; 225,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,29; 731,01</t>
+          <t>78,84; 733,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 101,5</t>
+          <t>0,92; 102,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 49,29</t>
+          <t>-33,03; 44,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 99,5</t>
+          <t>-13,76; 110,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,47; 115,3</t>
+          <t>21,39; 111,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 53,7</t>
+          <t>-22,76; 52,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 142,27</t>
+          <t>25,89; 175,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,01</t>
+          <t>3,63; 8,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,03</t>
+          <t>1,58; 6,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 13,63</t>
+          <t>4,77; 13,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,81</t>
+          <t>1,96; 10,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 4,67</t>
+          <t>-3,26; 4,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 7,58</t>
+          <t>-0,77; 8,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,97</t>
+          <t>3,64; 8,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,98</t>
+          <t>0,12; 4,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,57</t>
+          <t>3,58; 9,89</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>227,06%</t>
+          <t>237,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,71; 344,99</t>
+          <t>74,46; 313,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,18; 234,53</t>
+          <t>33,78; 224,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,4; 441,26</t>
+          <t>97,16; 445,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 88,38</t>
+          <t>11,64; 86,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 38,34</t>
+          <t>-20,48; 39,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 58,29</t>
+          <t>-4,52; 72,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,1; 121,57</t>
+          <t>37,17; 121,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 69,24</t>
+          <t>1,29; 66,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,96; 124,35</t>
+          <t>39,24; 131,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>6,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,78</t>
+          <t>0,77; 8,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,01</t>
+          <t>-1,52; 5,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,88</t>
+          <t>2,23; 9,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 13,92</t>
+          <t>5,4; 13,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,71</t>
+          <t>-1,31; 6,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 10,15</t>
+          <t>3,64; 11,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,64</t>
+          <t>4,32; 9,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,82</t>
+          <t>-0,06; 4,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,78</t>
+          <t>3,61; 9,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,05; 111,83</t>
+          <t>7,3; 112,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 77,83</t>
+          <t>-15,92; 70,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,16; 149,18</t>
+          <t>22,29; 132,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,72; 112,1</t>
+          <t>33,07; 111,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 54,65</t>
+          <t>-7,19; 55,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 80,49</t>
+          <t>22,1; 92,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,9; 93,47</t>
+          <t>33,0; 95,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 44,58</t>
+          <t>-0,44; 49,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,14; 84,72</t>
+          <t>26,41; 87,17</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>10,37</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>10,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 7,09</t>
+          <t>-2,31; 6,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 8,15</t>
+          <t>-0,64; 8,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 13,48</t>
+          <t>6,32; 15,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 15,43</t>
+          <t>4,65; 14,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 9,2</t>
+          <t>-1,21; 9,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,72; 14,69</t>
+          <t>5,55; 14,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,67</t>
+          <t>2,58; 9,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,59</t>
+          <t>0,6; 7,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 12,33</t>
+          <t>7,68; 14,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 54,44</t>
+          <t>-13,63; 50,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 62,39</t>
+          <t>-4,08; 64,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 94,75</t>
+          <t>34,95; 123,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,22; 75,11</t>
+          <t>17,45; 72,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 43,35</t>
+          <t>-4,95; 44,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,4; 73,43</t>
+          <t>21,7; 73,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,59; 54,99</t>
+          <t>12,56; 56,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 44,67</t>
+          <t>2,58; 40,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 66,99</t>
+          <t>35,65; 82,8</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>7,61</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 13,3</t>
+          <t>-0,12; 13,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,83</t>
+          <t>-6,15; 6,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 14,55</t>
+          <t>1,49; 13,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,58; 19,0</t>
+          <t>5,16; 19,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 14,66</t>
+          <t>0,33; 14,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 13,7</t>
+          <t>1,76; 14,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,12</t>
+          <t>4,8; 14,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,51</t>
+          <t>-0,33; 9,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,74</t>
+          <t>3,1; 10,99</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 43,89</t>
+          <t>-0,14; 44,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 25,21</t>
+          <t>-16,32; 22,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,5; 47,75</t>
+          <t>3,61; 43,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,53; 46,9</t>
+          <t>10,82; 49,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,68; 36,27</t>
+          <t>0,82; 34,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,44; 34,55</t>
+          <t>3,44; 34,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,19; 37,47</t>
+          <t>11,67; 38,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 25,5</t>
+          <t>-0,81; 24,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7,82; 31,91</t>
+          <t>7,12; 30,03</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,92</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>4,39</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>14,49; 30,27</t>
+          <t>13,66; 29,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,77; 16,53</t>
+          <t>0,81; 15,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,51</t>
+          <t>1,32; 15,27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,03; 15,26</t>
+          <t>1,23; 15,2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 6,18</t>
+          <t>-7,4; 6,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 28,93</t>
+          <t>-4,09; 7,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,42; 20,23</t>
+          <t>9,24; 20,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 8,77</t>
+          <t>-1,76; 8,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,41; 27,33</t>
+          <t>-0,24; 9,32</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30,15; 77,74</t>
+          <t>28,18; 74,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1,55; 41,39</t>
+          <t>1,35; 37,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3,59; 38,36</t>
+          <t>2,99; 39,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,84; 24,49</t>
+          <t>1,96; 24,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 10,14</t>
+          <t>-10,83; 11,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 48,35</t>
+          <t>-5,97; 12,26</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,88; 38,62</t>
+          <t>15,87; 37,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 16,77</t>
+          <t>-3,1; 16,02</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,83; 49,61</t>
+          <t>-0,44; 17,88</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,53; 22,55</t>
+          <t>5,8; 21,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 13,75</t>
+          <t>-1,28; 14,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 10,8</t>
+          <t>-5,25; 11,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,31; 20,95</t>
+          <t>7,88; 20,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 11,15</t>
+          <t>-2,16; 12,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,3; 14,08</t>
+          <t>1,69; 13,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,33; 19,5</t>
+          <t>9,32; 19,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,37; 10,37</t>
+          <t>-0,52; 10,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,32</t>
+          <t>0,52; 10,24</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,36; 37,38</t>
+          <t>8,2; 36,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 23,11</t>
+          <t>-1,77; 24,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 18,06</t>
+          <t>-7,56; 18,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,67; 30,76</t>
+          <t>10,13; 29,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 16,45</t>
+          <t>-2,74; 17,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,1; 20,69</t>
+          <t>2,32; 19,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,65; 29,05</t>
+          <t>12,88; 28,68</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,52; 15,45</t>
+          <t>-0,7; 15,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,35; 15,55</t>
+          <t>0,7; 15,34</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,81</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,61</t>
+          <t>5,84; 9,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,29</t>
+          <t>3,64; 7,42</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,19</t>
+          <t>10,15; 14,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,55</t>
+          <t>7,98; 12,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,37</t>
+          <t>2,72; 7,32</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,74; 23,49</t>
+          <t>8,79; 12,82</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,68</t>
+          <t>7,51; 10,55</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,74</t>
+          <t>3,81; 6,82</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,13</t>
+          <t>9,7; 12,93</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>31,36; 57,97</t>
+          <t>31,42; 59,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>19,65; 44,51</t>
+          <t>20,11; 45,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23,44; 77,44</t>
+          <t>54,61; 86,75</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25,13; 43,69</t>
+          <t>25,46; 43,08</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,55; 25,51</t>
+          <t>8,66; 25,58</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,86; 79,74</t>
+          <t>28,39; 44,74</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,29; 46,5</t>
+          <t>31,01; 46,19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14,9; 29,39</t>
+          <t>15,58; 29,81</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34,48; 72,37</t>
+          <t>39,77; 56,61</t>
         </is>
       </c>
     </row>
